--- a/artfynd/A 8641-2025 artfynd.xlsx
+++ b/artfynd/A 8641-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,379 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122862743</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57629</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skyddszon alsumpskog, Skäralid, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>394476</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6212694</v>
+      </c>
+      <c r="S3" t="n">
+        <v>75</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz, Per Muhr, Inger Persson, Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122862756</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57848</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skyddszon alsumpskog, Skäralid, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>394476</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6212694</v>
+      </c>
+      <c r="S4" t="n">
+        <v>75</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz, Per Muhr, Inger Persson, Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122862734</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57484</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skyddszon alsumpskog, Skäralid, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>394476</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6212694</v>
+      </c>
+      <c r="S5" t="n">
+        <v>75</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>trumning</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz, Per Muhr, Inger Persson, Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8641-2025 artfynd.xlsx
+++ b/artfynd/A 8641-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122862743</v>
+        <v>122862756</v>
       </c>
       <c r="B3" t="n">
-        <v>57629</v>
+        <v>57848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,20 +799,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -820,11 +820,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -911,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122862756</v>
+        <v>122862734</v>
       </c>
       <c r="B4" t="n">
-        <v>57848</v>
+        <v>57484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,20 +919,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -944,7 +940,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
@@ -1005,6 +1005,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>trumning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122862734</v>
+        <v>122862743</v>
       </c>
       <c r="B5" t="n">
-        <v>57484</v>
+        <v>57629</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,16 +1052,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1066,7 +1071,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1129,11 +1134,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>trumning</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 8641-2025 artfynd.xlsx
+++ b/artfynd/A 8641-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122862756</v>
+        <v>122862734</v>
       </c>
       <c r="B3" t="n">
-        <v>57848</v>
+        <v>57484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,20 +799,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -820,7 +820,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -831,7 +835,7 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skyddszon alsumpskog, Skäralid, Sk</t>
+          <t>Skyddszon blandsumpskog, Skäralid, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -881,6 +885,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>trumning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122862734</v>
+        <v>122862743</v>
       </c>
       <c r="B4" t="n">
-        <v>57484</v>
+        <v>57629</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,16 +932,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -942,7 +951,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -955,7 +964,7 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skyddszon alsumpskog, Skäralid, Sk</t>
+          <t>Skyddszon blandsumpskog, Skäralid, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1005,11 +1014,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>trumning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122862743</v>
+        <v>122862756</v>
       </c>
       <c r="B5" t="n">
-        <v>57629</v>
+        <v>57848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,20 +1052,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1069,11 +1073,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skyddszon alsumpskog, Skäralid, Sk</t>
+          <t>Skyddszon blandsumpskog, Skäralid, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">

--- a/artfynd/A 8641-2025 artfynd.xlsx
+++ b/artfynd/A 8641-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1158,6 +1158,337 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122975041</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57907</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skyddszon blandsumpskog, Skäralid, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>394476</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6212694</v>
+      </c>
+      <c r="S6" t="n">
+        <v>75</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122975947</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58123</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skyddszon blandsumpskog, Skäralid, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>394476</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6212694</v>
+      </c>
+      <c r="S7" t="n">
+        <v>75</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122975931</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97311</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skyddszon blandsumpskog, Skäralid, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>394476</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6212694</v>
+      </c>
+      <c r="S8" t="n">
+        <v>75</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8641-2025 artfynd.xlsx
+++ b/artfynd/A 8641-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1489,6 +1489,227 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123049190</v>
+      </c>
+      <c r="B9" t="n">
+        <v>95128</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skyddszon blandsumpskog, Skäralid, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>394476</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6212694</v>
+      </c>
+      <c r="S9" t="n">
+        <v>75</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123049491</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skyddszon blandsumpskog, Skäralid, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>394476</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6212694</v>
+      </c>
+      <c r="S10" t="n">
+        <v>75</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8641-2025 artfynd.xlsx
+++ b/artfynd/A 8641-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122862734</v>
+        <v>122862743</v>
       </c>
       <c r="B3" t="n">
-        <v>57484</v>
+        <v>57629</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -885,11 +885,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>trumning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122862743</v>
+        <v>122862756</v>
       </c>
       <c r="B4" t="n">
-        <v>57629</v>
+        <v>57848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,20 +923,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -949,11 +944,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
@@ -1040,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122862756</v>
+        <v>122862734</v>
       </c>
       <c r="B5" t="n">
-        <v>57848</v>
+        <v>57484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,20 +1043,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1073,7 +1064,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
@@ -1134,6 +1129,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>trumning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1387,7 +1387,7 @@
         <v>122975931</v>
       </c>
       <c r="B8" t="n">
-        <v>97311</v>
+        <v>97319</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123049190</v>
+        <v>123049491</v>
       </c>
       <c r="B9" t="n">
-        <v>95128</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,31 +1503,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1579,7 +1587,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1598,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123049491</v>
+        <v>123049190</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>95136</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,39 +1617,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1694,6 +1693,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8641-2025 artfynd.xlsx
+++ b/artfynd/A 8641-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122862743</v>
+        <v>122862734</v>
       </c>
       <c r="B3" t="n">
-        <v>57629</v>
+        <v>57484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -885,6 +885,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>trumning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1031,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122862734</v>
+        <v>122862743</v>
       </c>
       <c r="B5" t="n">
-        <v>57484</v>
+        <v>57629</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,16 +1052,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1066,7 +1071,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1129,11 +1134,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>trumning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122975041</v>
+        <v>122975947</v>
       </c>
       <c r="B6" t="n">
-        <v>57907</v>
+        <v>58123</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,28 +1172,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103001</v>
+        <v>103042</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
@@ -1238,12 +1242,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122975947</v>
+        <v>122975041</v>
       </c>
       <c r="B7" t="n">
-        <v>58123</v>
+        <v>57907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,32 +1286,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103042</v>
+        <v>103001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123049491</v>
+        <v>123049190</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>95136</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,39 +1503,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1587,6 +1579,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1605,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123049190</v>
+        <v>123049491</v>
       </c>
       <c r="B10" t="n">
-        <v>95136</v>
+        <v>57494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,31 +1610,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1693,7 +1694,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8641-2025 artfynd.xlsx
+++ b/artfynd/A 8641-2025 artfynd.xlsx
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122862756</v>
+        <v>122862743</v>
       </c>
       <c r="B4" t="n">
-        <v>57848</v>
+        <v>57629</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,20 +928,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -949,7 +949,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
@@ -1036,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122862743</v>
+        <v>122862756</v>
       </c>
       <c r="B5" t="n">
-        <v>57629</v>
+        <v>57848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,20 +1052,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1069,11 +1073,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
@@ -1160,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122975947</v>
+        <v>122975041</v>
       </c>
       <c r="B6" t="n">
-        <v>58123</v>
+        <v>57907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,32 +1172,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103042</v>
+        <v>103001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
@@ -1242,12 +1238,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122975041</v>
+        <v>122975931</v>
       </c>
       <c r="B7" t="n">
-        <v>57907</v>
+        <v>97319</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,35 +1282,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103001</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1352,12 +1344,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,6 +1358,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1384,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122975931</v>
+        <v>122975947</v>
       </c>
       <c r="B8" t="n">
-        <v>97319</v>
+        <v>58123</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,31 +1389,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>103042</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1472,7 +1473,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123049190</v>
+        <v>123049491</v>
       </c>
       <c r="B9" t="n">
-        <v>95136</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,31 +1503,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1579,7 +1587,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1598,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123049491</v>
+        <v>123049190</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>95136</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,39 +1617,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1694,6 +1693,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8641-2025 artfynd.xlsx
+++ b/artfynd/A 8641-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122862734</v>
+        <v>122862756</v>
       </c>
       <c r="B3" t="n">
-        <v>57484</v>
+        <v>57848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,20 +799,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -820,11 +820,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -885,11 +881,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>trumning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122862743</v>
+        <v>122862734</v>
       </c>
       <c r="B4" t="n">
-        <v>57629</v>
+        <v>57484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,16 +923,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -951,7 +942,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1014,6 +1005,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>trumning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122862756</v>
+        <v>122862743</v>
       </c>
       <c r="B5" t="n">
-        <v>57848</v>
+        <v>57629</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,20 +1048,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1073,7 +1069,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
@@ -1160,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122975041</v>
+        <v>122975931</v>
       </c>
       <c r="B6" t="n">
-        <v>57907</v>
+        <v>97319</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,35 +1172,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103001</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1238,12 +1234,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,6 +1248,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1270,10 +1267,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122975931</v>
+        <v>122975041</v>
       </c>
       <c r="B7" t="n">
-        <v>97319</v>
+        <v>57907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,31 +1279,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>103001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1344,12 +1345,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,7 +1359,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123049491</v>
+        <v>123049190</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>95136</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,39 +1503,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1587,6 +1579,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1605,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123049190</v>
+        <v>123049491</v>
       </c>
       <c r="B10" t="n">
-        <v>95136</v>
+        <v>57494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,31 +1610,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1693,7 +1694,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8641-2025 artfynd.xlsx
+++ b/artfynd/A 8641-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122862756</v>
+        <v>122862734</v>
       </c>
       <c r="B3" t="n">
-        <v>57848</v>
+        <v>57487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,20 +799,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -820,7 +820,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -881,6 +885,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>trumning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122862734</v>
+        <v>122862756</v>
       </c>
       <c r="B4" t="n">
-        <v>57484</v>
+        <v>57851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,20 +928,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -940,11 +949,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
@@ -1005,11 +1010,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>trumning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1039,7 @@
         <v>122862743</v>
       </c>
       <c r="B5" t="n">
-        <v>57629</v>
+        <v>57632</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122975931</v>
+        <v>122975041</v>
       </c>
       <c r="B6" t="n">
-        <v>97319</v>
+        <v>57910</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,31 +1172,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>103001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1234,12 +1238,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,7 +1252,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1267,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122975041</v>
+        <v>122975947</v>
       </c>
       <c r="B7" t="n">
-        <v>57907</v>
+        <v>58126</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,28 +1282,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103001</v>
+        <v>103042</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
@@ -1345,12 +1352,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122975947</v>
+        <v>122975931</v>
       </c>
       <c r="B8" t="n">
-        <v>58123</v>
+        <v>97322</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,39 +1396,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103042</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1473,6 +1472,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123049190</v>
+        <v>123049491</v>
       </c>
       <c r="B9" t="n">
-        <v>95136</v>
+        <v>57497</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,31 +1503,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1579,7 +1587,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1598,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123049491</v>
+        <v>123049190</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>95139</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,39 +1617,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1694,6 +1693,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8641-2025 artfynd.xlsx
+++ b/artfynd/A 8641-2025 artfynd.xlsx
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122862756</v>
+        <v>122862743</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>57632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,20 +928,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -949,7 +949,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
@@ -1036,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122862743</v>
+        <v>122862756</v>
       </c>
       <c r="B5" t="n">
-        <v>57632</v>
+        <v>57851</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,20 +1052,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1069,11 +1073,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122975947</v>
+        <v>122975931</v>
       </c>
       <c r="B7" t="n">
-        <v>58126</v>
+        <v>97324</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,39 +1282,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103042</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1366,6 +1358,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1384,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122975931</v>
+        <v>122975947</v>
       </c>
       <c r="B8" t="n">
-        <v>97322</v>
+        <v>58126</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,31 +1389,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>103042</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1472,7 +1473,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>123049190</v>
       </c>
       <c r="B10" t="n">
-        <v>95139</v>
+        <v>95141</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 8641-2025 artfynd.xlsx
+++ b/artfynd/A 8641-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122862734</v>
+        <v>122862743</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -885,11 +885,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>trumning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122862743</v>
+        <v>122862734</v>
       </c>
       <c r="B4" t="n">
-        <v>57632</v>
+        <v>57487</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,16 +927,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -951,7 +946,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1014,6 +1009,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>trumning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1160,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122975041</v>
+        <v>122975947</v>
       </c>
       <c r="B6" t="n">
-        <v>57910</v>
+        <v>58126</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,28 +1172,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103001</v>
+        <v>103042</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
@@ -1238,12 +1242,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,7 +1277,7 @@
         <v>122975931</v>
       </c>
       <c r="B7" t="n">
-        <v>97324</v>
+        <v>97330</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1377,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122975947</v>
+        <v>122975041</v>
       </c>
       <c r="B8" t="n">
-        <v>58126</v>
+        <v>57910</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,32 +1393,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103042</v>
+        <v>103001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1608,7 +1608,7 @@
         <v>123049190</v>
       </c>
       <c r="B10" t="n">
-        <v>95141</v>
+        <v>95147</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 8641-2025 artfynd.xlsx
+++ b/artfynd/A 8641-2025 artfynd.xlsx
@@ -1160,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122975041</v>
+        <v>122975947</v>
       </c>
       <c r="B6" t="n">
-        <v>57910</v>
+        <v>58132</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,28 +1172,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103001</v>
+        <v>103042</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
@@ -1238,12 +1242,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122975947</v>
+        <v>122975931</v>
       </c>
       <c r="B7" t="n">
-        <v>58126</v>
+        <v>97350</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,39 +1286,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103042</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1366,6 +1362,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1384,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122975931</v>
+        <v>122975041</v>
       </c>
       <c r="B8" t="n">
-        <v>97333</v>
+        <v>57916</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,31 +1393,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>103001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1458,12 +1459,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,7 +1473,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123049190</v>
+        <v>123049491</v>
       </c>
       <c r="B9" t="n">
-        <v>95150</v>
+        <v>57503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,31 +1503,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1579,7 +1587,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1598,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123049491</v>
+        <v>123049190</v>
       </c>
       <c r="B10" t="n">
-        <v>57497</v>
+        <v>95167</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,39 +1617,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1694,6 +1693,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8641-2025 artfynd.xlsx
+++ b/artfynd/A 8641-2025 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123049491</v>
+        <v>123049190</v>
       </c>
       <c r="B9" t="n">
-        <v>57503</v>
+        <v>95173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,39 +1503,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1587,6 +1579,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1605,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123049190</v>
+        <v>123049491</v>
       </c>
       <c r="B10" t="n">
-        <v>95167</v>
+        <v>57506</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,31 +1610,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1693,7 +1694,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8641-2025 artfynd.xlsx
+++ b/artfynd/A 8641-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,6 +1710,231 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124909378</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56965</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skyddszon blandsumpskog, Långarödsbäcken, Skäralid, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>394476</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6212694</v>
+      </c>
+      <c r="S11" t="n">
+        <v>75</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz, Thomas Arnström, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124909631</v>
+      </c>
+      <c r="B12" t="n">
+        <v>109906</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Valeriana dioica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skyddszon blandsumpskog, Långarödsbäcken, Skäralid, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>394476</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6212694</v>
+      </c>
+      <c r="S12" t="n">
+        <v>75</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz, Thomas Arnström, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8641-2025 artfynd.xlsx
+++ b/artfynd/A 8641-2025 artfynd.xlsx
@@ -1712,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124909378</v>
+        <v>124909631</v>
       </c>
       <c r="B11" t="n">
-        <v>56965</v>
+        <v>109906</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,39 +1724,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102954</v>
+        <v>221049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Valeriana dioica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1808,6 +1804,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1826,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124909631</v>
+        <v>124909378</v>
       </c>
       <c r="B12" t="n">
-        <v>109906</v>
+        <v>56965</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,35 +1835,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221049</v>
+        <v>102954</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Valeriana dioica</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1918,7 +1919,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8641-2025 artfynd.xlsx
+++ b/artfynd/A 8641-2025 artfynd.xlsx
@@ -1712,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124909631</v>
+        <v>124909378</v>
       </c>
       <c r="B11" t="n">
-        <v>109906</v>
+        <v>56965</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,35 +1724,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221049</v>
+        <v>102954</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Valeriana dioica</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1804,7 +1808,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1823,10 +1826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124909378</v>
+        <v>124909631</v>
       </c>
       <c r="B12" t="n">
-        <v>56965</v>
+        <v>109906</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,39 +1838,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102954</v>
+        <v>221049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Valeriana dioica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1919,6 +1918,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8641-2025 artfynd.xlsx
+++ b/artfynd/A 8641-2025 artfynd.xlsx
@@ -1715,7 +1715,7 @@
         <v>124909378</v>
       </c>
       <c r="B11" t="n">
-        <v>56965</v>
+        <v>57053</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz, Thomas Arnström, Per Muhr</t>
+          <t>Petra Borgcrantz, Per Muhr, Thomas Arnström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1829,7 +1829,7 @@
         <v>124909631</v>
       </c>
       <c r="B12" t="n">
-        <v>109906</v>
+        <v>110092</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 8641-2025 artfynd.xlsx
+++ b/artfynd/A 8641-2025 artfynd.xlsx
@@ -1712,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124909378</v>
+        <v>124909631</v>
       </c>
       <c r="B11" t="n">
-        <v>57053</v>
+        <v>110092</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,39 +1724,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102954</v>
+        <v>221049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Valeriana dioica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1808,6 +1804,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1819,17 +1816,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz, Per Muhr, Thomas Arnström</t>
+          <t>Petra Borgcrantz, Thomas Arnström, Per Muhr</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124909631</v>
+        <v>124909378</v>
       </c>
       <c r="B12" t="n">
-        <v>110092</v>
+        <v>57053</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,35 +1835,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221049</v>
+        <v>102954</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Valeriana dioica</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1918,7 +1919,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8641-2025 artfynd.xlsx
+++ b/artfynd/A 8641-2025 artfynd.xlsx
@@ -1717,11 +1717,6 @@
       <c r="B11" t="n">
         <v>110092</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>VU</t>
@@ -1827,11 +1822,6 @@
       </c>
       <c r="B12" t="n">
         <v>57053</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
